--- a/output/北塩原村_アンケート結果報告書_点検結果.xlsx
+++ b/output/北塩原村_アンケート結果報告書_点検結果.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>報告書に「本調査では当該指標を測定していない」旨を明記する。計画側では、行政データ（地域活動・スポーツ教室の参加者数等）による代替指標への振替を村と協議する（docs/北塩原村_調査票確定に伴うクロス集計対応方針.md の S-1）</t>
+          <t>報告書に「本調査では当該指標を測定していない」旨を明記する。計画側では、行政データ（地域活動・スポーツ教室の参加者数等）による代替指標への振替を村と協議する（docs/北塩原村_調査票確定に伴うクロス集計対応方針.md の Ｓ-1）</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>村に照会する。Ａ型は既にリスクR-25・確認事項M-4として登録済み。就労選択支援は令和7年10月開始であり、令和7年度の給付実績に現れるはずの時期である点も併せて確認する</t>
+          <t>村に照会する。Ａ型は既にリスクR-25・確認事項Ｍ-4として登録済み。就労選択支援は令和7年10月開始であり、令和7年度の給付実績に現れるはずの時期である点も併せて確認する</t>
         </is>
       </c>
     </row>
